--- a/Data/RemapDrafts/BarbaraRemapDraft.xlsx
+++ b/Data/RemapDrafts/BarbaraRemapDraft.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCD04F6-742E-4EDE-9476-E59E15D5CA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AB8E55-150C-4204-B378-3BFE425BAD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5F0387E8-ECD3-4B89-A1B8-741FD14AA159}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{5F0387E8-ECD3-4B89-A1B8-741FD14AA159}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.0 - Barbara to Summertime" sheetId="1" r:id="rId1"/>
-    <sheet name="V4.0 - Summertime to Barbara" sheetId="2" r:id="rId2"/>
+    <sheet name="Credits" sheetId="3" r:id="rId1"/>
+    <sheet name="V4.0 - Barbara to Summertime" sheetId="1" r:id="rId2"/>
+    <sheet name="V4.0 - Summertime to Barbara" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.0 - Barbara to Summertime'!$A$1:$D$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 - Summertime to Barbara'!$A$1:$D$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 - Barbara to Summertime'!$A$1:$D$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'V4.0 - Summertime to Barbara'!$A$1:$D$88</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -194,13 +195,22 @@
   </si>
   <si>
     <t>BarbaraSummertime's left middle arm</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
+  </si>
+  <si>
+    <t>Authors</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +221,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -234,14 +260,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -594,17 +624,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CB41FD-28D9-43B5-9AB1-E51171278F35}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{F800D0BF-F018-43D3-BD05-AF7A1109550B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7904AEFC-678B-4B51-930B-224E6469B1A4}">
   <dimension ref="A1:D104"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="114.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="114.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -618,7 +679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -629,7 +690,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -637,7 +698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -645,7 +706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -656,7 +717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -664,7 +725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -672,7 +733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -686,7 +747,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -700,7 +761,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -708,7 +769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -716,7 +777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -724,7 +785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -732,7 +793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -740,7 +801,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -748,7 +809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -756,7 +817,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -764,7 +825,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -772,7 +833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -780,7 +841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -788,7 +849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -796,7 +857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -807,7 +868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -818,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -832,7 +893,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -846,7 +907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -857,7 +918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -868,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -882,7 +943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -896,7 +957,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -907,7 +968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -921,7 +982,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -935,7 +996,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -949,7 +1010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -963,7 +1024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -974,7 +1035,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -988,7 +1049,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1002,7 +1063,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1013,7 +1074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1024,7 +1085,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1038,7 +1099,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1052,7 +1113,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1063,7 +1124,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1074,7 +1135,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1082,7 +1143,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1090,7 +1151,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1098,7 +1159,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1109,7 +1170,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1117,7 +1178,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1125,7 +1186,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1133,7 +1194,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1144,7 +1205,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1158,7 +1219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1169,7 +1230,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1183,7 +1244,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1194,7 +1255,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1202,7 +1263,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1210,7 +1271,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1218,7 +1279,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1226,7 +1287,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1234,7 +1295,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1242,7 +1303,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1250,7 +1311,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1258,7 +1319,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1266,7 +1327,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1274,7 +1335,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1282,7 +1343,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1290,7 +1351,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1298,7 +1359,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1306,7 +1367,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1314,7 +1375,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -1322,7 +1383,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1330,7 +1391,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1338,7 +1399,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1346,7 +1407,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -1357,7 +1418,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1365,7 +1426,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1373,7 +1434,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -1381,7 +1442,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1389,7 +1450,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1397,7 +1458,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -1405,7 +1466,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -1413,7 +1474,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -1421,7 +1482,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -1429,7 +1490,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -1437,7 +1498,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -1445,7 +1506,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -1453,7 +1514,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -1461,7 +1522,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -1469,7 +1530,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -1477,7 +1538,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -1485,7 +1546,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -1493,7 +1554,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -1501,7 +1562,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -1509,7 +1570,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
@@ -1517,7 +1578,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>94</v>
       </c>
@@ -1525,7 +1586,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>95</v>
       </c>
@@ -1533,7 +1594,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>96</v>
       </c>
@@ -1544,7 +1605,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>97</v>
       </c>
@@ -1552,7 +1613,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>98</v>
       </c>
@@ -1560,7 +1621,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>99</v>
       </c>
@@ -1568,7 +1629,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>100</v>
       </c>
@@ -1576,7 +1637,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>101</v>
       </c>
@@ -1584,7 +1645,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>102</v>
       </c>
@@ -1601,18 +1662,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27BBF372-5BA5-473C-A296-872102C13533}">
   <dimension ref="A1:D88"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="83.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="83.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1626,7 +1687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1634,7 +1695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1642,7 +1703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1650,7 +1711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1658,7 +1719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1666,7 +1727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1674,7 +1735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1682,7 +1743,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1690,7 +1751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1698,7 +1759,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1706,7 +1767,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1714,7 +1775,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1722,7 +1783,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1730,7 +1791,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1738,7 +1799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1746,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1754,7 +1815,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1762,7 +1823,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1770,7 +1831,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1778,7 +1839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1789,7 +1850,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1800,7 +1861,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1811,7 +1872,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1822,7 +1883,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1833,7 +1894,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1844,7 +1905,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1855,7 +1916,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1866,7 +1927,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1877,7 +1938,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1888,7 +1949,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1899,7 +1960,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1910,7 +1971,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1918,7 +1979,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1929,7 +1990,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1937,7 +1998,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1948,7 +2009,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1956,7 +2017,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1964,7 +2025,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1972,7 +2033,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1980,7 +2041,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1988,7 +2049,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1996,7 +2057,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2004,7 +2065,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2012,7 +2073,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2020,7 +2081,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2028,7 +2089,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2036,7 +2097,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2044,7 +2105,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2052,7 +2113,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2060,7 +2121,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2068,7 +2129,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2076,7 +2137,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2084,7 +2145,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2092,7 +2153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2100,7 +2161,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2108,7 +2169,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2116,7 +2177,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2124,7 +2185,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2132,7 +2193,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2140,7 +2201,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2151,7 +2212,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2159,7 +2220,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2167,7 +2228,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -2175,7 +2236,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -2183,7 +2244,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -2191,7 +2252,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2199,7 +2260,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -2207,7 +2268,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -2215,7 +2276,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -2223,7 +2284,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -2231,7 +2292,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2239,7 +2300,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2247,7 +2308,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2255,7 +2316,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2263,7 +2324,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2271,7 +2332,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2279,7 +2340,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -2287,7 +2348,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2295,7 +2356,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2303,7 +2364,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2311,7 +2372,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2319,7 +2380,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -2327,7 +2388,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -2335,7 +2396,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2346,7 +2407,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2354,7 +2415,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2362,7 +2423,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
